--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -2991,7 +2991,7 @@
         <v>129129337</v>
       </c>
       <c r="B23" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>129129417</v>
       </c>
       <c r="B24" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120678604</v>
+        <v>120681123</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659359</v>
+        <v>658982</v>
       </c>
       <c r="R2" t="n">
-        <v>6550532</v>
+        <v>6550586</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,62 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120678832</v>
+        <v>120682705</v>
       </c>
       <c r="B3" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659359</v>
+        <v>658982</v>
       </c>
       <c r="R3" t="n">
-        <v>6550532</v>
+        <v>6550586</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120679374</v>
+        <v>126435814</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,42 +909,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Snickartorp S-W, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659359</v>
+        <v>659000</v>
       </c>
       <c r="R4" t="n">
-        <v>6550532</v>
+        <v>6550708</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +975,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>återfynd på känd lokal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,77 +994,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Johan Abenius</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Johan Abenius</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120679073</v>
+        <v>120678769</v>
       </c>
       <c r="B5" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Kvarntorp, Kvarntorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659359</v>
+        <v>659060</v>
       </c>
       <c r="R5" t="n">
-        <v>6550532</v>
+        <v>6550442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1081,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,27 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120681958</v>
+        <v>120680024</v>
       </c>
       <c r="B6" t="n">
-        <v>94459</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,34 +1121,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snickartorp, Snickartorp, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659094</v>
+        <v>659359</v>
       </c>
       <c r="R6" t="n">
-        <v>6550658</v>
+        <v>6550532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,9 +1178,19 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,27 +1205,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120681784</v>
+        <v>120681745</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658982</v>
+        <v>659038</v>
       </c>
       <c r="R7" t="n">
-        <v>6550586</v>
+        <v>6550627</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,19 +1285,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,27 +1302,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120677194</v>
+        <v>120680764</v>
       </c>
       <c r="B8" t="n">
-        <v>94471</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,34 +1325,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659331</v>
+        <v>658939</v>
       </c>
       <c r="R8" t="n">
-        <v>6550537</v>
+        <v>6550661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,15 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120682420</v>
+        <v>120681262</v>
       </c>
       <c r="B9" t="n">
-        <v>94459</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,14 +1442,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snickartorp, Snickartorp, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659113</v>
+        <v>658959</v>
       </c>
       <c r="R9" t="n">
-        <v>6550612</v>
+        <v>6550666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,15 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120681262</v>
+        <v>120681958</v>
       </c>
       <c r="B10" t="n">
-        <v>94459</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,14 +1539,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Snickartorp, Snickartorp, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658959</v>
+        <v>659094</v>
       </c>
       <c r="R10" t="n">
-        <v>6550666</v>
+        <v>6550658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,55 +1605,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120682716</v>
+        <v>120682420</v>
       </c>
       <c r="B11" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Snickartorp, Snickartorp, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658982</v>
+        <v>659113</v>
       </c>
       <c r="R11" t="n">
-        <v>6550586</v>
+        <v>6550612</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,19 +1673,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,27 +1690,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120681745</v>
+        <v>120677194</v>
       </c>
       <c r="B12" t="n">
-        <v>94558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,34 +1713,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659038</v>
+        <v>659331</v>
       </c>
       <c r="R12" t="n">
-        <v>6550627</v>
+        <v>6550537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,15 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120680929</v>
+        <v>120674999</v>
       </c>
       <c r="B13" t="n">
-        <v>74641</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,34 +1810,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658982</v>
+        <v>659463</v>
       </c>
       <c r="R13" t="n">
-        <v>6550586</v>
+        <v>6550629</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,19 +1867,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,27 +1884,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120680237</v>
+        <v>120682467</v>
       </c>
       <c r="B14" t="n">
-        <v>103570</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,34 +1907,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Snickartorp, Snickartorp, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658917</v>
+        <v>659129</v>
       </c>
       <c r="R14" t="n">
-        <v>6550561</v>
+        <v>6550625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,19 +1964,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,12 +1981,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2112,12 +1996,7 @@
         <v>120681309</v>
       </c>
       <c r="B15" t="n">
-        <v>91362</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,15 +2100,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120683105</v>
+        <v>120701222</v>
       </c>
       <c r="B16" t="n">
-        <v>30075</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,37 +2111,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200985</v>
+        <v>3884</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Srm</t>
+          <t>Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>659170</v>
+        <v>658923</v>
       </c>
       <c r="R16" t="n">
-        <v>6550529</v>
+        <v>6550531</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,22 +2168,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,68 +2182,73 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120680764</v>
+        <v>120678832</v>
       </c>
       <c r="B17" t="n">
-        <v>94459</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658939</v>
+        <v>659359</v>
       </c>
       <c r="R17" t="n">
-        <v>6550661</v>
+        <v>6550532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,9 +2278,19 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,65 +2305,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120682705</v>
+        <v>120679073</v>
       </c>
       <c r="B18" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöängen, Sjöängen, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658982</v>
+        <v>659359</v>
       </c>
       <c r="R18" t="n">
-        <v>6550586</v>
+        <v>6550532</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2396,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2406,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,53 +2433,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120682467</v>
+        <v>129129337</v>
       </c>
       <c r="B19" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Snickartorp, Snickartorp, Srm</t>
+          <t>Sjöängen, Fituna, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>659129</v>
+        <v>659037</v>
       </c>
       <c r="R19" t="n">
-        <v>6550625</v>
+        <v>6550462</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,12 +2509,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,33 +2523,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120680024</v>
+        <v>129129417</v>
       </c>
       <c r="B20" t="n">
-        <v>96683</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,37 +2553,48 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>6031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ovelund, Ovelund, Srm</t>
+          <t>Sjöängen, Fituna, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659359</v>
+        <v>659017</v>
       </c>
       <c r="R20" t="n">
-        <v>6550532</v>
+        <v>6550491</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2719,22 +2618,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,67 +2632,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tore Söderqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120681123</v>
+        <v>120680929</v>
       </c>
       <c r="B21" t="n">
-        <v>94675</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sjöängen, Sjöängen, Srm</t>
@@ -2845,7 +2721,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2855,7 +2731,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,15 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120701222</v>
+        <v>120679374</v>
       </c>
       <c r="B22" t="n">
-        <v>91229</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,40 +2769,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3884</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöängen, Srm</t>
+          <t>Ovelund, Ovelund, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658923</v>
+        <v>659359</v>
       </c>
       <c r="R22" t="n">
-        <v>6550531</v>
+        <v>6550532</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2955,12 +2828,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,78 +2852,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129129337</v>
+        <v>120682716</v>
       </c>
       <c r="B23" t="n">
-        <v>92901</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöängen, Fituna, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659037</v>
+        <v>658982</v>
       </c>
       <c r="R23" t="n">
-        <v>6550462</v>
+        <v>6550586</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3064,12 +2940,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,29 +2964,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129129417</v>
+        <v>120681784</v>
       </c>
       <c r="B24" t="n">
-        <v>92234</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,48 +2993,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöängen, Fituna, Srm</t>
+          <t>Sjöängen, Sjöängen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659017</v>
+        <v>658982</v>
       </c>
       <c r="R24" t="n">
-        <v>6550491</v>
+        <v>6550586</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,12 +3047,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,22 +3071,439 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tore Söderqvist</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120678604</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ovelund, Ovelund, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>659359</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550532</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120683105</v>
+      </c>
+      <c r="B26" t="n">
+        <v>30288</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarntorp, Kvarntorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>659170</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6550529</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120680237</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sjöängen, Sjöängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>658917</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550561</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120680255</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sjöängen, Sjöängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>658915</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6550578</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43747-2024 artfynd.xlsx
+++ b/artfynd/A 43747-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126435814</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678769</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120680024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120680764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681262</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681958</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682420</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677194</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120674999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681309</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120701222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678832</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679073</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2539,6 +2629,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129337</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2648,6 +2743,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129417</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2755,6 +2855,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120680929</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679374</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2979,6 +3089,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682716</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3086,6 +3201,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681784</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,6 +3313,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678604</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683105</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3407,6 +3537,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120680237</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,8 +3639,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120680255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>